--- a/deploy/142_ENT_GARANTIAS_IV/69 GARANTIAS_IV.xlsx
+++ b/deploy/142_ENT_GARANTIAS_IV/69 GARANTIAS_IV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\deploy\142_ENT_GARANTIAS_IV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2C21DBC-D9DD-4C83-B713-51C0D3842072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4912E3-A7A3-439E-88E0-02386D564274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9610" yWindow="4460" windowWidth="24690" windowHeight="15950" xr2:uid="{8B9903A0-1318-49F7-BCD3-D97C11F4253C}"/>
+    <workbookView xWindow="4360" yWindow="8440" windowWidth="18430" windowHeight="10890" xr2:uid="{8B9903A0-1318-49F7-BCD3-D97C11F4253C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="12">
   <si>
     <t>OFICINA</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>000750</t>
+  </si>
+  <si>
+    <t>000111</t>
   </si>
 </sst>
 </file>
@@ -104,9 +110,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,8 +478,8 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
-        <v>775</v>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -494,8 +501,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
-        <v>780</v>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -517,8 +524,8 @@
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
-        <v>770</v>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -540,8 +547,8 @@
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>790</v>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -563,8 +570,8 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>111</v>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -586,8 +593,8 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>770</v>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -609,8 +616,8 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>750</v>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -632,8 +639,8 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>760</v>
+      <c r="B9" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -655,8 +662,8 @@
       <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10">
-        <v>750</v>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -678,8 +685,8 @@
       <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11">
-        <v>760</v>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C11">
         <v>3</v>
